--- a/public/templates/darschin-input-template.xlsx
+++ b/public/templates/darschin-input-template.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" r:id="R14d9facb75ea4d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="دروس" sheetId="2" r:id="R7bb06104e1b54585"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جلسات" sheetId="3" r:id="R749a264f0e854750"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="استادان" sheetId="4" r:id="Ra1d53181f6794eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="گروه‌های دانشجویی" sheetId="5" r:id="R3ce7fac2d73a4824"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فضاها" sheetId="6" r:id="Rac3d69183a07465d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجهیزات" sheetId="7" r:id="R434f78f1b3a44d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعارض‌ها" sheetId="8" r:id="R42b4a805fa4f48f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تنظیمات" sheetId="9" r:id="R213f4d68e00f42fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" r:id="Reebbc20897084535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="دروس" sheetId="2" r:id="R1ec831edd1074ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="جلسات" sheetId="3" r:id="R54943b1432d14f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="استادان" sheetId="4" r:id="R6e89cf5cbb364268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="گروه‌های دانشجویی" sheetId="5" r:id="Re8eac25b3e654ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فضاها" sheetId="6" r:id="Rd3027d1988174a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تجهیزات" sheetId="7" r:id="R65ccd7a34a4d4caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تعارض‌ها" sheetId="8" r:id="R0dfb208e34984a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تنظیمات" sheetId="9" r:id="Rd95edb6951e9428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مرجع کدها" sheetId="10" r:id="Ree5af436e8b149e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -36,8 +37,19 @@
       <x:sz val="11"/>
       <x:name val="Vazirmatn"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Vazirmatn"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Vazirmatn"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +61,21 @@
         <x:fgColor rgb="FF243B80"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243B80"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF2FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE9F8F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -57,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,6 +160,63 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -307,117 +391,827 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>درس‌چین — راهنمای تکمیل Excel</x:v>
+      </x:c>
+      <x:c r="B1" s="26"/>
+      <x:c r="C1" s="26"/>
+      <x:c r="D1" s="26"/>
+      <x:c r="E1" s="26"/>
+      <x:c r="F1" s="26"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="33" t="str">
+        <x:v>هدف</x:v>
+      </x:c>
+      <x:c r="B2" s="33" t="str">
+        <x:v>این فایل برای ورود گروه‌های درسی، جلسات، استادان، گروه‌های دانشجویی، فضاها، تجهیزات و قواعد به درس‌چین است.</x:v>
+      </x:c>
+      <x:c r="C2" s="33"/>
+      <x:c r="D2" s="33"/>
+      <x:c r="E2" s="33"/>
+      <x:c r="F2" s="33"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="33" t="str">
+        <x:v>ترتیب تکمیل</x:v>
+      </x:c>
+      <x:c r="B3" s="33" t="str">
+        <x:v>۱) تجهیزات و فضاها  ۲) استادان و گروه‌های دانشجویی  ۳) دروس  ۴) جلسات  ۵) تعارض‌ها  ۶) تنظیمات</x:v>
+      </x:c>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="14"/>
+      <x:c r="B4" s="14"/>
+      <x:c r="C4" s="44"/>
+      <x:c r="D4" s="44"/>
+      <x:c r="E4" s="44"/>
+      <x:c r="F4" s="44"/>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="24" t="str">
+        <x:v>قاعده</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
+        <x:v>معنی</x:v>
+      </x:c>
+      <x:c r="C5" s="24" t="str">
+        <x:v>کاربرد</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
+        <x:v>مثال درست</x:v>
+      </x:c>
+      <x:c r="E5" s="24" t="str">
+        <x:v>مثال نادرست</x:v>
+      </x:c>
+      <x:c r="F5" s="24" t="str">
+        <x:v>نکته</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="40" t="str">
+        <x:v>شناسه‌ها</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:v>id یک کلید فنی یکتا و بدون فاصله است.</x:v>
+      </x:c>
+      <x:c r="C6" s="40" t="str">
+        <x:v>برای اتصال ردیف‌ها به یکدیگر.</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="str">
+        <x:v>i-ahmadi یا c-math1-101</x:v>
+      </x:c>
+      <x:c r="E6" s="40" t="str">
+        <x:v>دکتر احمدی</x:v>
+      </x:c>
+      <x:c r="F6" s="40" t="str">
+        <x:v>عنوان خوانا را در ستون name یا label بنویسید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>شماره گروه</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:v>groupNumber عدد صحیح مثبت و در کل فایل یکتا است.</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:v>تشخیص ارائه مستقل درس.</x:v>
+      </x:c>
+      <x:c r="D7" s="40" t="str">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E7" s="40" t="str">
+        <x:v>101-الف</x:v>
+      </x:c>
+      <x:c r="F7" s="40" t="str">
+        <x:v>دو ارائه از یک درس باید شماره گروه متفاوت داشته باشند.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="40" t="str">
+        <x:v>هر ردیف جلسات</x:v>
+      </x:c>
+      <x:c r="B8" s="40" t="str">
+        <x:v>یک جلسه هفتگی مستقل از یک گروه درسی است.</x:v>
+      </x:c>
+      <x:c r="C8" s="40" t="str">
+        <x:v>جلسه نظری، عملی یا آزمایشگاه.</x:v>
+      </x:c>
+      <x:c r="D8" s="40" t="str">
+        <x:v>دو ردیف برای دو جلسه هفته</x:v>
+      </x:c>
+      <x:c r="E8" s="40" t="str">
+        <x:v>نوشتن دو زمان در یک سلول</x:v>
+      </x:c>
+      <x:c r="F8" s="40" t="str">
+        <x:v>courseId باید به id برگه دروس اشاره کند.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="40" t="str">
+        <x:v>روزهای ممنوع</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:v>کل روز برای آن استاد، گروه یا جلسه غیرقابل استفاده است.</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:v>قید سخت.</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>sun,tue</x:v>
+      </x:c>
+      <x:c r="E9" s="40" t="str">
+        <x:v>یکشنبه، سه‌شنبه</x:v>
+      </x:c>
+      <x:c r="F9" s="40" t="str">
+        <x:v>کد روزها در برگه مرجع کدها آمده است.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="40" t="str">
+        <x:v>بازه‌های ممنوع</x:v>
+      </x:c>
+      <x:c r="B10" s="40" t="str">
+        <x:v>فقط بازه مشخص از یک روز ممنوع است.</x:v>
+      </x:c>
+      <x:c r="C10" s="40" t="str">
+        <x:v>قید سخت جزئی.</x:v>
+      </x:c>
+      <x:c r="D10" s="40" t="str">
+        <x:v>sat:0,sun:2</x:v>
+      </x:c>
+      <x:c r="E10" s="40" t="str">
+        <x:v>شنبه صبح</x:v>
+      </x:c>
+      <x:c r="F10" s="40" t="str">
+        <x:v>عدد بازه از صفر شروع می‌شود؛ sat:0 یعنی شنبه بازه اول.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="40" t="str">
+        <x:v>روز یا بازه نامطلوب</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>مجاز است ولی جریمه ایجاد می‌کند.</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>ترجیح نرم.</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:v>tue یا tue:4</x:v>
+      </x:c>
+      <x:c r="E11" s="40" t="str">
+        <x:v>ثبت در ستون unavailable</x:v>
+      </x:c>
+      <x:c r="F11" s="40" t="str">
+        <x:v>اگر واقعاً غیرممکن است، آن را ممنوع ثبت کنید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="40" t="str">
+        <x:v>زمان ثابت</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="str">
+        <x:v>جلسه باید دقیقاً در روز و بازه مشخص شروع شود.</x:v>
+      </x:c>
+      <x:c r="C12" s="40" t="str">
+        <x:v>برای زمان از پیش تعیین‌شده.</x:v>
+      </x:c>
+      <x:c r="D12" s="40" t="str">
+        <x:v>sat:1</x:v>
+      </x:c>
+      <x:c r="E12" s="40" t="str">
+        <x:v>شنبه</x:v>
+      </x:c>
+      <x:c r="F12" s="40" t="str">
+        <x:v>خالی بگذارید تا حل‌کننده زمان را انتخاب کند.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="40" t="str">
+        <x:v>اتاق ثابت</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:v>جلسه فقط در یک اتاق مشخص مجاز است.</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:v>قید سخت فضا.</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="str">
+        <x:v>r-comp1</x:v>
+      </x:c>
+      <x:c r="E13" s="40" t="str">
+        <x:v>سایت رایانه ۱</x:v>
+      </x:c>
+      <x:c r="F13" s="40" t="str">
+        <x:v>شناسه اتاق را از برگه فضاها بردارید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="40" t="str">
+        <x:v>اتاق‌های ترجیحی</x:v>
+      </x:c>
+      <x:c r="B14" s="40" t="str">
+        <x:v>فهرست رتبه‌بندی‌شده از اتاق‌های مطلوب.</x:v>
+      </x:c>
+      <x:c r="C14" s="40" t="str">
+        <x:v>ترجیح نرم.</x:v>
+      </x:c>
+      <x:c r="D14" s="40" t="str">
+        <x:v>r-a101,r-a202</x:v>
+      </x:c>
+      <x:c r="E14" s="40" t="str">
+        <x:v>A101,A202</x:v>
+      </x:c>
+      <x:c r="F14" s="40" t="str">
+        <x:v>ترتیب نوشتن همان ترتیب اولویت است.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="40" t="str">
+        <x:v>تجهیز الزامی</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>نبود آن اتاق را غیرقابل استفاده می‌کند.</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>قید سخت.</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>computers</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="str">
+        <x:v>رایانه</x:v>
+      </x:c>
+      <x:c r="F15" s="40" t="str">
+        <x:v>شناسه تجهیز را از برگه تجهیزات بردارید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="40" t="str">
+        <x:v>تجهیز ترجیحی</x:v>
+      </x:c>
+      <x:c r="B16" s="40" t="str">
+        <x:v>نبود آن فقط جریمه ایجاد می‌کند.</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="str">
+        <x:v>ترجیح نرم.</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="str">
+        <x:v>projector</x:v>
+      </x:c>
+      <x:c r="E16" s="40"/>
+      <x:c r="F16" s="40" t="str">
+        <x:v>برای نیاز قطعی از requiredEquipmentIds استفاده کنید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>مدت جلسه</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>تعداد بازه‌های آموزشی متوالی.</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>برای جلسه‌های طولانی.</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>180 دقیقه</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="str">
+        <x:v>مدت بر حسب تعداد بازه است، نه دقیقه.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="40" t="str">
+        <x:v>عبور از وقفه</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>جلسه چندبازه‌ای می‌تواند پس از وقفه ادامه یابد.</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>برای کارگاه یا آزمایشگاه.</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="str">
+        <x:v>بله</x:v>
+      </x:c>
+      <x:c r="F18" s="40" t="str">
+        <x:v>مدت وقفه جزو زمان آموزشی حساب نمی‌شود.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="40" t="str">
+        <x:v>الگوی هفته</x:v>
+      </x:c>
+      <x:c r="B19" s="40" t="str">
+        <x:v>هر هفته، فقط فرد یا فقط زوج.</x:v>
+      </x:c>
+      <x:c r="C19" s="40" t="str">
+        <x:v>اشتراک زمان و اتاق در هفته‌های متفاوت.</x:v>
+      </x:c>
+      <x:c r="D19" s="40" t="str">
+        <x:v>all / odd / even</x:v>
+      </x:c>
+      <x:c r="E19" s="40" t="str">
+        <x:v>هرهفته</x:v>
+      </x:c>
+      <x:c r="F19" s="40" t="str">
+        <x:v>کدها را دقیقاً مطابق برگه مرجع کدها بنویسید.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="40" t="str">
+        <x:v>جلسه اجباری</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="str">
+        <x:v>تخصیص‌نیافتن آن نتیجه را ناموفق می‌کند.</x:v>
+      </x:c>
+      <x:c r="C20" s="40" t="str">
+        <x:v>برای جلسه غیرقابل حذف.</x:v>
+      </x:c>
+      <x:c r="D20" s="40" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="E20" s="40" t="str">
+        <x:v>الزامی</x:v>
+      </x:c>
+      <x:c r="F20" s="40" t="str">
+        <x:v>در برگه جلسات ستون required.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="40" t="str">
+        <x:v>تعارض سخت</x:v>
+      </x:c>
+      <x:c r="B21" s="40" t="str">
+        <x:v>دو درس نباید هم‌زمان شوند.</x:v>
+      </x:c>
+      <x:c r="C21" s="40" t="str">
+        <x:v>برای دانشجویان یا سیاست آموزشی مشترک.</x:v>
+      </x:c>
+      <x:c r="D21" s="40" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="E21" s="40" t="str">
+        <x:v>سخت</x:v>
+      </x:c>
+      <x:c r="F21" s="40" t="str">
+        <x:v>شدت برای تعارض سخت استفاده نمی‌شود.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="40" t="str">
+        <x:v>تعارض نرم</x:v>
+      </x:c>
+      <x:c r="B22" s="40" t="str">
+        <x:v>هم‌زمانی مجاز ولی جریمه‌دار است.</x:v>
+      </x:c>
+      <x:c r="C22" s="40" t="str">
+        <x:v>ترجیح مدیریتی.</x:v>
+      </x:c>
+      <x:c r="D22" s="40" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="E22" s="40" t="str">
+        <x:v>نرم</x:v>
+      </x:c>
+      <x:c r="F22" s="40" t="str">
+        <x:v>ستون weight شدت را مشخص می‌کند.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="44"/>
+      <x:c r="B23" s="44"/>
+      <x:c r="C23" s="44"/>
+      <x:c r="D23" s="44"/>
+      <x:c r="E23" s="44"/>
+      <x:c r="F23" s="44"/>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="43" t="str">
+        <x:v>چک‌لیست پیش از ورود</x:v>
+      </x:c>
+      <x:c r="B24" s="43" t="str">
+        <x:v>همه idها یکتا هستند.</x:v>
+      </x:c>
+      <x:c r="C24" s="43" t="str">
+        <x:v>courseIdها در برگه دروس وجود دارند.</x:v>
+      </x:c>
+      <x:c r="D24" s="43" t="str">
+        <x:v>شناسه استاد، گروه، اتاق و تجهیز معتبر است.</x:v>
+      </x:c>
+      <x:c r="E24" s="43" t="str">
+        <x:v>شماره گروه تکراری نیست.</x:v>
+      </x:c>
+      <x:c r="F24" s="43" t="str">
+        <x:v>نام برگه‌ها و عنوان ستون‌ها تغییر نکرده است.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="65" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>نکته</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>شرح</x:v>
+      <x:c r="A1" s="38" t="str">
+        <x:v>نوع</x:v>
+      </x:c>
+      <x:c r="B1" s="38" t="str">
+        <x:v>کد</x:v>
+      </x:c>
+      <x:c r="C1" s="38" t="str">
+        <x:v>معنی فارسی</x:v>
+      </x:c>
+      <x:c r="D1" s="38" t="str">
+        <x:v>کجا استفاده می‌شود</x:v>
+      </x:c>
+      <x:c r="E1" s="38" t="str">
+        <x:v>مثال</x:v>
+      </x:c>
+      <x:c r="F1" s="38" t="str">
+        <x:v>توضیح</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>۱</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>نام برگه‌ها و عنوان ستون‌ها را تغییر ندهید.</x:v>
+      <x:c r="A2" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B2" s="40" t="str">
+        <x:v>sat</x:v>
+      </x:c>
+      <x:c r="C2" s="40" t="str">
+        <x:v>شنبه</x:v>
+      </x:c>
+      <x:c r="D2" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E2" s="40" t="str">
+        <x:v>sat:0</x:v>
+      </x:c>
+      <x:c r="F2" s="40" t="str">
+        <x:v>عدد پس از دونقطه شماره بازه از صفر است.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>۲</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>شماره گروه عدد صحیح مثبت و در کل فایل یکتا است.</x:v>
-      </x:c>
+      <x:c r="A3" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B3" s="40" t="str">
+        <x:v>sun</x:v>
+      </x:c>
+      <x:c r="C3" s="40" t="str">
+        <x:v>یکشنبه</x:v>
+      </x:c>
+      <x:c r="D3" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E3" s="40" t="str">
+        <x:v>sun:2</x:v>
+      </x:c>
+      <x:c r="F3" s="40"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
-        <x:v>۳</x:v>
-      </x:c>
-      <x:c r="B4" s="14" t="str">
-        <x:v>هر ردیف در برگه جلسات یک جلسه هفتگی مستقل است.</x:v>
-      </x:c>
+      <x:c r="A4" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B4" s="40" t="str">
+        <x:v>mon</x:v>
+      </x:c>
+      <x:c r="C4" s="40" t="str">
+        <x:v>دوشنبه</x:v>
+      </x:c>
+      <x:c r="D4" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E4" s="40" t="str">
+        <x:v>mon</x:v>
+      </x:c>
+      <x:c r="F4" s="40"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
-        <x:v>۴</x:v>
-      </x:c>
-      <x:c r="B5" s="14" t="str">
-        <x:v>شناسه روزها: sat, sun, mon, tue, wed, thu. زمان: sat:1</x:v>
-      </x:c>
+      <x:c r="A5" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>tue</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>سه‌شنبه</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>tue:4</x:v>
+      </x:c>
+      <x:c r="F5" s="40"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>۵</x:v>
-      </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>فهرست‌ها را با ویرگول جدا کنید. اتاق‌های ترجیحی به ترتیب نوشته می‌شوند.</x:v>
-      </x:c>
+      <x:c r="A6" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:v>wed</x:v>
+      </x:c>
+      <x:c r="C6" s="40" t="str">
+        <x:v>چهارشنبه</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E6" s="40" t="str">
+        <x:v>wed</x:v>
+      </x:c>
+      <x:c r="F6" s="40"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>۶</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>weekPattern یکی از all, odd, even است؛ kind یکی از hard, soft.</x:v>
-      </x:c>
+      <x:c r="A7" s="40" t="str">
+        <x:v>روز</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:v>thu</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:v>پنج‌شنبه</x:v>
+      </x:c>
+      <x:c r="D7" s="40" t="str">
+        <x:v>dayIds و قواعد زمان</x:v>
+      </x:c>
+      <x:c r="E7" s="40" t="str">
+        <x:v>thu:1</x:v>
+      </x:c>
+      <x:c r="F7" s="40"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14"/>
-      <x:c r="B8" s="14"/>
+      <x:c r="A8" s="40" t="str">
+        <x:v>الگوی هفته</x:v>
+      </x:c>
+      <x:c r="B8" s="40" t="str">
+        <x:v>all</x:v>
+      </x:c>
+      <x:c r="C8" s="40" t="str">
+        <x:v>هر هفته</x:v>
+      </x:c>
+      <x:c r="D8" s="40" t="str">
+        <x:v>weekPattern</x:v>
+      </x:c>
+      <x:c r="E8" s="40" t="str">
+        <x:v>all</x:v>
+      </x:c>
+      <x:c r="F8" s="40"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14"/>
-      <x:c r="B9" s="14"/>
+      <x:c r="A9" s="40" t="str">
+        <x:v>الگوی هفته</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:v>odd</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:v>هفته‌های فرد</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>weekPattern</x:v>
+      </x:c>
+      <x:c r="E9" s="40" t="str">
+        <x:v>odd</x:v>
+      </x:c>
+      <x:c r="F9" s="40"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14"/>
-      <x:c r="B10" s="14"/>
+      <x:c r="A10" s="40" t="str">
+        <x:v>الگوی هفته</x:v>
+      </x:c>
+      <x:c r="B10" s="40" t="str">
+        <x:v>even</x:v>
+      </x:c>
+      <x:c r="C10" s="40" t="str">
+        <x:v>هفته‌های زوج</x:v>
+      </x:c>
+      <x:c r="D10" s="40" t="str">
+        <x:v>weekPattern</x:v>
+      </x:c>
+      <x:c r="E10" s="40" t="str">
+        <x:v>even</x:v>
+      </x:c>
+      <x:c r="F10" s="40"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14"/>
-      <x:c r="B11" s="14"/>
+      <x:c r="A11" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>lecture</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>کلاس نظری</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:v>roomType</x:v>
+      </x:c>
+      <x:c r="E11" s="40" t="str">
+        <x:v>lecture</x:v>
+      </x:c>
+      <x:c r="F11" s="40"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="14"/>
-      <x:c r="B12" s="14"/>
+      <x:c r="A12" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="str">
+        <x:v>computer</x:v>
+      </x:c>
+      <x:c r="C12" s="40" t="str">
+        <x:v>سایت رایانه</x:v>
+      </x:c>
+      <x:c r="D12" s="40" t="str">
+        <x:v>roomType</x:v>
+      </x:c>
+      <x:c r="E12" s="40" t="str">
+        <x:v>computer</x:v>
+      </x:c>
+      <x:c r="F12" s="40"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="14"/>
-      <x:c r="B13" s="14"/>
+      <x:c r="A13" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:v>laboratory</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:v>آزمایشگاه</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="str">
+        <x:v>roomType</x:v>
+      </x:c>
+      <x:c r="E13" s="40" t="str">
+        <x:v>laboratory</x:v>
+      </x:c>
+      <x:c r="F13" s="40"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14"/>
-      <x:c r="B14" s="14"/>
+      <x:c r="A14" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B14" s="40" t="str">
+        <x:v>workshop</x:v>
+      </x:c>
+      <x:c r="C14" s="40" t="str">
+        <x:v>کارگاه</x:v>
+      </x:c>
+      <x:c r="D14" s="40" t="str">
+        <x:v>roomType</x:v>
+      </x:c>
+      <x:c r="E14" s="40" t="str">
+        <x:v>workshop</x:v>
+      </x:c>
+      <x:c r="F14" s="40"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="14"/>
-      <x:c r="B15" s="14"/>
+      <x:c r="A15" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>studio</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>آتلیه / استودیو</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>roomType</x:v>
+      </x:c>
+      <x:c r="E15" s="40" t="str">
+        <x:v>studio</x:v>
+      </x:c>
+      <x:c r="F15" s="40"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="14"/>
-      <x:c r="B16" s="14"/>
+      <x:c r="A16" s="40" t="str">
+        <x:v>نوع فضا</x:v>
+      </x:c>
+      <x:c r="B16" s="40" t="str">
+        <x:v>any</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="str">
+        <x:v>هر فضای سازگار</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="str">
+        <x:v>roomType در درس یا جلسه</x:v>
+      </x:c>
+      <x:c r="E16" s="40" t="str">
+        <x:v>any</x:v>
+      </x:c>
+      <x:c r="F16" s="40" t="str">
+        <x:v>برای خود اتاق استفاده نشود.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="14"/>
-      <x:c r="B17" s="14"/>
+      <x:c r="A17" s="40" t="str">
+        <x:v>نوع تعارض</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>سخت؛ هم‌زمانی ممنوع</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>kind</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="F17" s="40"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="14"/>
-      <x:c r="B18" s="14"/>
+      <x:c r="A18" s="40" t="str">
+        <x:v>نوع تعارض</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>نرم؛ هم‌زمانی جریمه‌دار</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>kind</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="str">
+        <x:v>soft</x:v>
+      </x:c>
+      <x:c r="F18" s="40"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="14"/>
-      <x:c r="B19" s="14"/>
+      <x:c r="A19" s="40" t="str">
+        <x:v>مقدار منطقی</x:v>
+      </x:c>
+      <x:c r="B19" s="40" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C19" s="40" t="str">
+        <x:v>بله</x:v>
+      </x:c>
+      <x:c r="D19" s="40" t="str">
+        <x:v>required و allowBreakCrossing</x:v>
+      </x:c>
+      <x:c r="E19" s="40" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="F19" s="40"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="14"/>
-      <x:c r="B20" s="14"/>
+      <x:c r="A20" s="40" t="str">
+        <x:v>مقدار منطقی</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="C20" s="40" t="str">
+        <x:v>خیر</x:v>
+      </x:c>
+      <x:c r="D20" s="40" t="str">
+        <x:v>required و allowBreakCrossing</x:v>
+      </x:c>
+      <x:c r="E20" s="40" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="F20" s="40"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -820,11 +1614,20 @@
       <x:c r="M20" s="14"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="J2:J200">
       <x:formula1>"lecture,computer,laboratory,workshop,studio,any"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M2:M200">
+      <x:formula1>"all,odd,even"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J500">
+      <x:formula1>"lecture,computer,laboratory,workshop,studio,any"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M500">
       <x:formula1>"all,odd,even"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1367,12 +2170,18 @@
       <x:c r="T20" s="14"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="I2:I1000">
       <x:formula1>"lecture,computer,laboratory,workshop,studio,any"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="L2:L1000">
       <x:formula1>"all,odd,even"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="H2:H1000">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M1000">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
